--- a/stories/arbres/ATOM-REL.CON.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Prune est au parc avec papa. Papa s'assoit sur le banc. Prune joue près de la marelle. La craie est douce sous les doigts. Idriss court vers la marelle. Idriss bouscule Prune. Prune sent un choc. Son cœur bat vite. Prune dit : stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa. Prune marche vers le banc. Papa est son parent au parc. Prune rejoint son parent au parc. Elle dit : Idriss m'a bousculée. Papa l'écoute. Papa dit : tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main. Prune souffle doucement. Le banc est calme.</t>
+          <t>Prune est au parc avec papa. Papa s'assoit sur le banc. Prune joue près de la marelle. La craie est douce sous les doigts. Idriss court vers la marelle. Idriss bouscule Prune. Prune sent un choc. Son cœur bat vite. Stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa. Prune marche vers le banc. Papa est son parent au parc. Prune rejoint son parent au parc. Idriss m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main. Prune souffle doucement. Le banc est calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Prune est au parc avec papa. Papa s'assoit sur le banc. Prune joue près de la marelle. La craie est douce sous les doigts. Idriss court vers la marelle. Idriss bouscule Prune. Prune sent un choc. Son cœur bat vite.
+enfant-f|Stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa.
+narrateur|Prune marche vers le banc. Papa est son parent au parc. Prune rejoint son parent au parc.
+narrateur|Idriss m'a bousculée. Papa l'écoute.
+papa|Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main.
+narrateur|Prune souffle doucement. Le banc est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Prune. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Prune a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Prune boit une gorgée d'eau. Papa garde sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 narrateur|Prune souffle doucement. Le banc est calme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1508,7 @@
           <t>narrateur|Un camarade bouscule Prune. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1680,11 @@
           <t>narrateur|Prune a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1852,7 @@
           <t>narrateur|Prune boit une gorgée d'eau. Papa garde sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prune dit stop au parc</t>
+          <t>La craie de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La craie poudre la marelle. Mila pose le caillou. Aniss arrive trop vite. Elle dit stop, s'éloigne, rejoint papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Prune est au parc avec papa. Papa s'assoit sur le banc. Prune joue près de la marelle. La craie est douce sous les doigts. Idriss court vers la marelle. Idriss bouscule Prune. Prune sent un choc. Son cœur bat vite. Stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa. Prune marche vers le banc. Papa est son parent au parc. Prune rejoint son parent au parc. Idriss m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main. Prune souffle doucement. Le banc est calme.</t>
+          <t>La craie blanche poudre les carrés. Un petit caillou gris attend au milieu. La poussière de craie est douce. Elle colle un peu aux doigts. Un oiseau saute près du carré. Le banc sent le bois chaud. Papa pose le sac près du banc. La gourde cliquette dans le sac. Mila, la marelle est pour toi. Le caillou t'attend. En ce moment, Mila s'accroupit. Elle prend le petit caillou. Il est lisse, un peu chaud. Il est gris, papa. Oui. Tu le poses dans un carré ? Mila pose le caillou. La craie fait un petit nuage. Bravo. C'est du bon travail. Le carré est blanc. Oui. Il est tout poudreux. Aniss arrive trop vite. Mila sent un choc. Son cœur bat vite. Stop. Elle fait un pas de côté. Elle s'éloigne. S'éloigner, c'est marcher vers papa. Mila marche vers le banc. Papa est son parent au parc. Mila rejoint son parent au parc. Aniss m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Bravo, Mila. Donne-moi ta main. Papa lui tient la main. La main de papa est tiède. Mon cœur bat. On souffle ? Mila souffle doucement. Le banc est calme. Tu restes près de moi. Je suis ton parent au parc. Tu veux un peu d'eau ? Oui, papa. Mila boit une petite gorgée. L'eau est fraîche. La craie reste sur les carrés. Le caillou attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Prune est au parc avec papa. Papa s'assoit sur le banc. Prune joue près de la marelle. La craie est douce sous les doigts. Idriss court vers la marelle. Idriss bouscule Prune. Prune sent un choc. Son cœur bat vite.
-enfant-f|Stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa.
-narrateur|Prune marche vers le banc. Papa est son parent au parc. Prune rejoint son parent au parc.
-narrateur|Idriss m'a bousculée. Papa l'écoute.
-papa|Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main.
-narrateur|Prune souffle doucement. Le banc est calme.</t>
+          <t>narrateur|La craie blanche poudre les carrés.
+narrateur|Un petit caillou gris attend au milieu.
+narrateur|La poussière de craie est douce.
+narrateur|Elle colle un peu aux doigts.
+narrateur|Un oiseau saute près du carré.
+narrateur|Le banc sent le bois chaud.
+narrateur|Papa pose le sac près du banc.
+narrateur|La gourde cliquette dans le sac.
+papa|Mila, la marelle est pour toi.
+papa|Le caillou t'attend.
+narrateur|En ce moment, Mila s'accroupit.
+narrateur|Elle prend le petit caillou.
+narrateur|Il est lisse, un peu chaud.
+enfant-f|Il est gris, papa.
+papa|Oui.
+papa|Tu le poses dans un carré ?
+narrateur|Mila pose le caillou.
+narrateur|La craie fait un petit nuage.
+papa|Bravo.
+papa|C'est du bon travail.
+enfant-f|Le carré est blanc.
+papa|Oui.
+papa|Il est tout poudreux.
+narrateur|Aniss arrive trop vite.
+narrateur|Mila sent un choc.
+narrateur|Son cœur bat vite.
+enfant-f|Stop.
+narrateur|Elle fait un pas de côté.
+narrateur|Elle s'éloigne.
+narrateur|S'éloigner, c'est marcher vers papa.
+narrateur|Mila marche vers le banc.
+narrateur|Papa est son parent au parc.
+narrateur|Mila rejoint son parent au parc.
+enfant-f|Aniss m'a bousculée.
+narrateur|Papa l'écoute.
+papa|Tu as dit stop.
+papa|Tu t'es éloignée.
+papa|Tu es venue vers moi.
+papa|Bravo, Mila.
+papa|Donne-moi ta main.
+narrateur|Papa lui tient la main.
+narrateur|La main de papa est tiède.
+enfant-f|Mon cœur bat.
+papa|On souffle ?
+narrateur|Mila souffle doucement.
+narrateur|Le banc est calme.
+papa|Tu restes près de moi.
+papa|Je suis ton parent au parc.
+papa|Tu veux un peu d'eau ?
+enfant-f|Oui, papa.
+narrateur|Mila boit une petite gorgée.
+narrateur|L'eau est fraîche.
+narrateur|La craie reste sur les carrés.
+narrateur|Le caillou attend encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Prune. Que fait-elle ?</t>
+          <t>Un camarade bouscule Mila. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,10 +1565,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Prune. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Un camarade bouscule Mila.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Prune a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.</t>
+          <t>Mila a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Tu es venue vers moi. Bravo. Je suis près de toi. Tu as fini de souffler ? Oui, papa. Mila essuie la craie sur son pantalon. La poussière est blanche, toute douce. C'est du bon travail, Mila.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,7 +1737,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Prune a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.</t>
+          <t>narrateur|Mila a dit stop.
+narrateur|Elle a su s'éloigner.
+narrateur|Elle a rejoint son parent au parc.
+papa|Tu es venue vers moi.
+papa|Bravo.
+papa|Je suis près de toi.
+papa|Tu as fini de souffler ?
+enfant-f|Oui, papa.
+narrateur|Mila essuie la craie sur son pantalon.
+narrateur|La poussière est blanche, toute douce.
+papa|C'est du bon travail, Mila.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1709,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Prune boit une gorgée d'eau. Papa garde sa main.</t>
+          <t>Papa ouvre la gourde. L'eau fait un petit bruit. Tu bois une gorgée ? Oui. Mila boit une gorgée d'eau. Donne-moi ta main. Papa garde sa main. On reste sur le banc ? Oui, papa. Le caillou reste sur le carré. La craie brille un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1849,10 +1919,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Prune boit une gorgée d'eau. Papa garde sa main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa ouvre la gourde.
+narrateur|L'eau fait un petit bruit.
+papa|Tu bois une gorgée ?
+enfant-f|Oui.
+narrateur|Mila boit une gorgée d'eau.
+papa|Donne-moi ta main.
+narrateur|Papa garde sa main.
+papa|On reste sur le banc ?
+enfant-f|Oui, papa.
+narrateur|Le caillou reste sur le carré.
+narrateur|La craie brille un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1877,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis venue. Bravo, Mila. Tu as fait du bon travail. La craie poudre encore les carrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2017,10 +2096,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|J'ai dit stop.
+enfant-f|Je suis venue.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|La craie poudre encore les carrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2039,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La craie blanche poudre les carrés. Un petit caillou gris attend au milieu. La poussière de craie est douce. Elle colle un peu aux doigts. Un oiseau saute près du carré. Le banc sent le bois chaud. Papa pose le sac près du banc. La gourde cliquette dans le sac. Mila, la marelle est pour toi. Le caillou t'attend. En ce moment, Mila s'accroupit. Elle prend le petit caillou. Il est lisse, un peu chaud. Il est gris, papa. Oui. Tu le poses dans un carré ? Mila pose le caillou. La craie fait un petit nuage. Bravo. C'est du bon travail. Le carré est blanc. Oui. Il est tout poudreux. Aniss arrive trop vite. Mila sent un choc. Son cœur bat vite. Stop. Elle fait un pas de côté. Elle s'éloigne. S'éloigner, c'est marcher vers papa. Mila marche vers le banc. Papa est son parent au parc. Mila rejoint son parent au parc. Aniss m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Bravo, Mila. Donne-moi ta main. Papa lui tient la main. La main de papa est tiède. Mon cœur bat. On souffle ? Mila souffle doucement. Le banc est calme. Tu restes près de moi. Je suis ton parent au parc. Tu veux un peu d'eau ? Oui, papa. Mila boit une petite gorgée. L'eau est fraîche. La craie reste sur les carrés. Le caillou attend encore.</t>
+          <t>La craie blanche poudre les carrés. Un petit caillou gris attend au milieu. La poussière de craie est douce. Elle colle un peu aux doigts. Un oiseau saute près du carré. Le banc sent le bois chaud. Papa pose le sac près du banc. La gourde cliquette dans le sac. Mila, la marelle est pour toi. Le caillou t'attend. En ce moment, Mila s'accroupit. Elle prend le petit caillou. Il est lisse, un peu chaud. Il est gris, papa. Oui. Tu le poses dans un carré ? Mila pose le caillou. La craie fait un petit nuage. Bravo. Le carré est blanc. Oui. Il est tout poudreux. Aniss arrive trop vite. Mila sent un choc. Son cœur bat vite. Stop. Elle fait un pas de côté. Elle s'éloigne. S'éloigner, c'est marcher vers papa. Mila marche vers le banc. Papa est son parent au parc. Mila rejoint son parent au parc. Aniss m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Bravo, Mila. Donne-moi ta main. Papa lui tient la main. La main de papa est tiède. Mon cœur bat. On souffle ? Mila souffle doucement. Le banc est calme. Tu restes près de moi. Je suis ton parent au parc. Tu veux un peu d'eau ? Oui, papa. Mila boit une petite gorgée. L'eau est fraîche. La craie reste sur les carrés. Le caillou attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Prune est au parc avec papa. Papa s'assoit sur le banc. Prune joue près de la marelle. La craie est douce sous les doigts. Idriss court vers la marelle. Idriss bouscule Prune. Prune sent un choc. Son cœur bat vite. Prune dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa. Prune marche vers le banc. Papa est son parent au parc. Prune rejoint son parent au parc. Elle dit : Idriss m'a bousculée. Papa l'écoute. Papa dit : tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main. Prune souffle doucement. Le banc est calme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La craie blanche poudre les carrés. Un petit caillou gris attend au milieu. La poussière de craie est douce. Elle colle un peu aux doigts. Un oiseau saute près du carré. Le banc sent le bois chaud. Papa pose le sac près du banc. La gourde cliquette dans le sac. Mila, la marelle est pour toi. Le caillou t'attend. En ce moment, Mila s'accroupit. Elle prend le petit caillou. Il est lisse, un peu chaud. Il est gris, papa. Oui. Tu le poses dans un carré ? Mila pose le caillou. La craie fait un petit nuage. Bravo. Le carré est blanc. Oui. Il est tout poudreux. Aniss arrive trop vite. Mila sent un choc. Son cœur bat vite. Stop. Elle fait un pas de côté. Elle s'éloigne. S'éloigner, c'est marcher vers papa. Mila marche vers le banc. Papa est son parent au parc. Mila rejoint son parent au parc. Aniss m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Bravo, Mila. Donne-moi ta main. Papa lui tient la main. La main de papa est tiède. Mon cœur bat. On souffle ? Mila souffle doucement. Le banc est calme. Tu restes près de moi. Je suis ton parent au parc. Tu veux un peu d'eau ? Oui, papa. Mila boit une petite gorgée. L'eau est fraîche. La craie reste sur les carrés. Le caillou attend encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1343,7 +1343,6 @@
 narrateur|Mila pose le caillou.
 narrateur|La craie fait un petit nuage.
 papa|Bravo.
-papa|C'est du bon travail.
 enfant-f|Le carré est blanc.
 papa|Oui.
 papa|Il est tout poudreux.
@@ -1414,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Un camarade bouscule Prune. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Mila. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1593,12 +1592,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Tu es venue vers moi. Bravo. Je suis près de toi. Tu as fini de souffler ? Oui, papa. Mila essuie la craie sur son pantalon. La poussière est blanche, toute douce. C'est du bon travail, Mila.</t>
+          <t>Mila a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Tu es venue vers moi. Bravo. Je suis près de toi. Tu as fini de souffler ? Oui, papa. Mila essuie la craie sur son pantalon. La poussière est blanche, toute douce.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Prune a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Tu es venue vers moi. Bravo. Je suis près de toi. Tu as fini de souffler ? Oui, papa. Mila essuie la craie sur son pantalon. La poussière est blanche, toute douce.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1746,8 +1745,7 @@
 papa|Tu as fini de souffler ?
 enfant-f|Oui, papa.
 narrateur|Mila essuie la craie sur son pantalon.
-narrateur|La poussière est blanche, toute douce.
-papa|C'est du bon travail, Mila.</t>
+narrateur|La poussière est blanche, toute douce.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1784,7 +1782,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Prune boit une gorgée d'eau. Papa garde sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa ouvre la gourde. L'eau fait un petit bruit. Tu bois une gorgée ? Oui. Mila boit une gorgée d'eau. Donne-moi ta main. Papa garde sa main. On reste sur le banc ? Oui, papa. Le caillou reste sur le carré. La craie brille un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1956,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis venue. Bravo, Mila. Tu as fait du bon travail. La craie poudre encore les carrés. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis venue. Bravo, Mila. La craie poudre encore les carrés.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis venue. Bravo, Mila. La craie poudre encore les carrés.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,9 +2097,7 @@
           <t>enfant-f|J'ai dit stop.
 enfant-f|Je suis venue.
 papa|Bravo, Mila.
-papa|Tu as fait du bon travail.
-narrateur|La craie poudre encore les carrés.
-narrateur|L'histoire est finie.</t>
+narrateur|La craie poudre encore les carrés.</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2163,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc, marelle à la craie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prune, Idriss, papa</t>
+          <t>Mila, Aniss, papa</t>
         </is>
       </c>
     </row>
